--- a/output/2026-09-05_13_Italia_Sicilia_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-05_13_Italia_Sicilia_Impiantistica_aspirazione_industriale.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Core business in target. Confermata da sito, LinkedIn, Facebook, PagineGialle/Bianche. Stesso numero cellulare (392 0770188) compare anche per 'Officine Marco D'Arpa' - possibile legame famigliare/societario tra le due aziende, da verificare umanamente per evitare sovrapposizioni commerciali.</t>
+          <t>Core business in target. Confermata da sito, LinkedIn, Facebook, PagineGialle/Bianche. Stesso numero cellulare (392 0770188) compare anche per 'Officine Marco D'Arpa' - possibile legame famigliare/societario tra le due aziende, da verificare umanamente per evitare sovrapposizioni commerciali. [DUPLICATO — vedi anche: 2026-09-05_12_Italia_Sicilia_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Confermata tramite sito e directory (Virgilio la classifica in categoria 'Aspirazione impianti'). Produttore/installatore di condotte, target adeguato come possibile rivenditore/partner tecnico.</t>
+          <t>Confermata tramite sito e directory (Virgilio la classifica in categoria 'Aspirazione impianti'). Produttore/installatore di condotte, target adeguato come possibile rivenditore/partner tecnico. [DUPLICATO — vedi anche: 2026-09-05_12_Italia_Sicilia_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -579,7 +579,6 @@
           <t>Trincair Condotti Srls</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Palermo (PA)</t>
@@ -590,7 +589,6 @@
           <t>Climatizzazione, ventilazione, estrazione e filtrazione aria - vendita materiali e componenti per canalizzazioni metalliche</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Esistenza confermata via PagineGialle. Nessun sito proprio individuato, contatti non reperibili nelle fonti pubbliche consultate - necessaria verifica diretta prima del contatto commerciale.</t>
